--- a/fapiao-templates/hechi_ca.xlsx
+++ b/fapiao-templates/hechi_ca.xlsx
@@ -10,9 +10,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="服务类型" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'服务类型'!$A$1:$A$43</definedName>
-  </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -2651,7 +2648,6 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="C71F"/>
-  <autoFilter ref="A1:A43"/>
   <conditionalFormatting sqref="A1:A65536">
     <cfRule type="duplicateValues" priority="1" dxfId="0"/>
   </conditionalFormatting>

--- a/fapiao-templates/hechi_ca.xlsx
+++ b/fapiao-templates/hechi_ca.xlsx
@@ -1835,24 +1835,6 @@
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
-  <dataValidations count="6">
-    <dataValidation sqref="B1:D1 B4:D4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1"/>
-    <dataValidation sqref="B2:D2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>Sheet1!$A:$A</formula1>
-    </dataValidation>
-    <dataValidation sqref="B20:D20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"买单报关,报关退税"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B21:D21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"包税,自主税号,自税递延,不包税"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B24" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"EUR,GBP,USD"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B17:D19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"是,否"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="257" horizontalDpi="203" verticalDpi="203"/>
 </worksheet>
@@ -2323,11 +2305,6 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="D24" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$A$1:$A$38</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
